--- a/app-factory-workplan-v2.xlsx
+++ b/app-factory-workplan-v2.xlsx
@@ -3185,7 +3185,7 @@
       </c>
       <c r="H12" s="82" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I12" s="82" t="n"/>
